--- a/artfynd/A 30472-2023 artfynd.xlsx
+++ b/artfynd/A 30472-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30472-2023 artfynd.xlsx
+++ b/artfynd/A 30472-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70263586</v>
+        <v>78626050</v>
       </c>
       <c r="B2" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100077</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,23 +708,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Forsaström, Falerumsvägen 850 m V Bråstorp, Sm</t>
+          <t>28, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563667.5289824163</v>
+        <v>563686</v>
       </c>
       <c r="R2" t="n">
-        <v>6449459.640833815</v>
+        <v>6449492</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2019-04-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2019-04-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sprang över länsvägen då jag kom med bil. Observerades därefter en kort stund vid vägkanten.</t>
+          <t>Stilla bredvid väg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,27 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Börkén</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Börkén</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78626053</v>
+        <v>78626051</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563683.9164244591</v>
+        <v>563683</v>
       </c>
       <c r="R3" t="n">
-        <v>6449492.075279719</v>
+        <v>6449490</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -921,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78626056</v>
+        <v>78626052</v>
       </c>
       <c r="B4" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563723.0519399942</v>
+        <v>563686</v>
       </c>
       <c r="R4" t="n">
-        <v>6449522.765522355</v>
+        <v>6449493</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1015,7 +996,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spelande</t>
+          <t>Stilla bredvid väg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78626050</v>
+        <v>78626053</v>
       </c>
       <c r="B5" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563686.0294137493</v>
+        <v>563684</v>
       </c>
       <c r="R5" t="n">
-        <v>6449492.109219713</v>
+        <v>6449492</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1163,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>78626052</v>
+        <v>78626056</v>
       </c>
       <c r="B6" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563686.0124752035</v>
+        <v>563723</v>
       </c>
       <c r="R6" t="n">
-        <v>6449493.163738756</v>
+        <v>6449523</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,7 +1228,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Stilla bredvid väg</t>
+          <t>Spelande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>78626055</v>
+        <v>81019593</v>
       </c>
       <c r="B7" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,38 +1266,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>28, Sm</t>
+          <t>Forsaström, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563724.8909031061</v>
+        <v>563694</v>
       </c>
       <c r="R7" t="n">
-        <v>6449506.973294831</v>
+        <v>6449473</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,24 +1337,14 @@
           <t>2019-04-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-04-24</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>23:50</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spelande</t>
+          <t>Identifiering av konfliktpunkter åt TRV.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,22 +1364,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Daniel Segerlind, Kajsa Mattsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>78626051</v>
+        <v>78626055</v>
       </c>
       <c r="B8" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,26 +1382,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>208250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1449,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563682.8938052232</v>
+        <v>563725</v>
       </c>
       <c r="R8" t="n">
-        <v>6449489.949271209</v>
+        <v>6449507</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1499,7 +1460,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Stilla bredvid väg</t>
+          <t>Spelande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,137 +1484,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>81019593</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>208249</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Rana temporaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Forsaström, Sm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>563694.258055724</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6449473.255114585</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Gärdserum</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2019-04-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2019-04-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Identifiering av konfliktpunkter åt TRV.</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Daniel Segerlind</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Daniel Segerlind, Kajsa Mattsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30472-2023 artfynd.xlsx
+++ b/artfynd/A 30472-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626050</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626051</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626052</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626053</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626056</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81019593</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,8 +1519,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626055</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>